--- a/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A2" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>omega_6_fatty_acids</t>
-        </is>
+      <c r="A3" t="str">
+        <v>omega_6_fatty_acids</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A4" t="str">
+        <v>selenium</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -584,10 +578,10 @@
       <c r="E4" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>2296</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A5" t="str">
+        <v>tomato</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -613,10 +605,10 @@
       <c r="E5" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
@@ -625,10 +617,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A6" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -642,12 +632,12 @@
       <c r="E6" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
       <c r="H6" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>103012</v>
       </c>
@@ -656,10 +646,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A7" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -673,10 +661,10 @@
       <c r="E7" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
@@ -685,10 +673,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>plant_protein_intake</t>
-        </is>
+      <c r="A8" t="str">
+        <v>plant_protein_intake</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -702,10 +688,10 @@
       <c r="E8" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>87841</v>
       </c>
@@ -714,10 +700,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A9" t="str">
+        <v>eggs</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -731,10 +715,10 @@
       <c r="E9" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>1812</v>
       </c>
@@ -743,10 +727,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A10" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>4</v>
@@ -767,7 +749,7 @@
         <v>3.723705085890995</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>75.48999999999999</v>
+        <v>75.49</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0.4983024239643537</v>
@@ -780,10 +762,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A11" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -797,10 +777,10 @@
       <c r="E11" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="2" t="n">
         <v>71421</v>
       </c>
@@ -809,10 +789,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A12" t="str">
+        <v>tea</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>5</v>
@@ -846,10 +824,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A13" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -863,12 +839,12 @@
       <c r="E13" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
@@ -877,10 +853,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A14" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>27</v>
@@ -914,10 +888,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A15" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
@@ -951,10 +923,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A16" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
@@ -988,10 +958,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A17" t="str">
+        <v>lutein</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
@@ -1025,10 +993,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A18" t="str">
+        <v>betaine</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1042,10 +1008,10 @@
       <c r="E18" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1054,10 +1020,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A19" t="str">
+        <v>choline</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1071,10 +1035,10 @@
       <c r="E19" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1083,10 +1047,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A20" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1100,12 +1062,12 @@
       <c r="E20" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>4112</v>
       </c>
@@ -1114,10 +1076,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A21" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>2</v>
@@ -1131,12 +1091,12 @@
       <c r="E21" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
       <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1145,10 +1105,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A22" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1162,10 +1120,10 @@
       <c r="E22" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1174,10 +1132,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A23" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>3</v>
@@ -1211,10 +1167,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A24" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1228,10 +1182,10 @@
       <c r="E24" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1240,10 +1194,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A25" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>3</v>
@@ -1277,10 +1229,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A26" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1294,10 +1244,10 @@
       <c r="E26" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1306,10 +1256,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A27" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1323,10 +1271,10 @@
       <c r="E27" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1335,10 +1283,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A28" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>3</v>
@@ -1359,7 +1305,7 @@
         <v>1611.24360139533</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>93.26000000000001</v>
+        <v>93.26</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>0.9220557767202346</v>
@@ -1372,10 +1318,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A29" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1389,10 +1333,10 @@
       <c r="E29" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="5"/>
       <c r="J29" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1401,173 +1345,177 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A30" t="str">
+        <v>calcium</v>
       </c>
       <c r="B30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1.0591852706547322</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0.9035715319777113</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1.241598919253702</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.37795762072777117</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2.9682519310279556</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0.9149861270491104</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>494621</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>vitamin_b1</v>
+      </c>
+      <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C31" s="3" t="n">
         <v>1.069616314941161</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.5119644960496699</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="4" t="n">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="2" t="n">
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4" t="n">
+        <v>85.51</v>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K31" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
+    <row r="32">
+      <c r="A32" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1.1271586532561868</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.9770670508204692</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1.300176468168491</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.6378314879402918</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.9918844610713744</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.10245798863837999</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>599592</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>processed_meat_intake</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1.149239018159417</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.9369737613162469</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1.409591575973965</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.6296319129363084</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>2.09765466731294</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>77.04</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.009426052809354803</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1766660</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>ultra_processed_food_intake</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>1.105391974364155</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0.9570496576537233</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>1.276599624884141</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>0.2118725844161015</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>5.767104886911577</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>80.59</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0.1598660025955668</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>563999</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1.149239018159417</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0.9369737613162469</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>1.409591575973965</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.6296319129363084</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>2.09765466731294</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>77.04000000000001</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.009426052809354803</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>1766660</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>5212</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1.159516828778204</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>1.049863300995226</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>1.289026327823149</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
-        <v>480347</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>3330</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="C34" s="3" t="n">
-        <v>1.198753536073191</v>
+        <v>1.1812816581299752</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.920382805616512</v>
+        <v>1.0754078661566628</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.575249959766321</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
+        <v>1.2975787138523882</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.6427321484843646</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.171085356668214</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0.21970887695697142</v>
+      </c>
       <c r="J34" s="2" t="n">
-        <v>1811</v>
+        <v>1127884</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>9</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A35" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1581,12 +1529,12 @@
       <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="4" t="n">
-        <v>92.65000000000001</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
+        <v>92.65</v>
+      </c>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1595,10 +1543,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>manganese</t>
-        </is>
+      <c r="A36" t="str">
+        <v>manganese</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1612,10 +1558,10 @@
       <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
@@ -1624,128 +1570,120 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A37" t="str">
+        <v>non_nutritive_sweetener_intake</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
+        <v>1.2763443304894546</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0.9973036417217132</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1.633459241320152</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" s="2" t="n">
+        <v>115981</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>potassium</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1.279067174104721</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.8702945807931509</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K38" s="2" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
+    <row r="39">
+      <c r="A39" t="str">
+        <v>dietary_protein_intake</v>
+      </c>
+      <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C39" s="3" t="n">
         <v>1.302388647984454</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.7565399032150474</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4" t="n">
+        <v>66.46</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="n">
+    <row r="40">
+      <c r="A40" t="str">
+        <v>yogurt</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1.307892083408092</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>1.029839375952533</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>777</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>non_nutritive_sweetener_intake</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>1.338814310253709</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>1.029919540076821</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>1.746586675661478</v>
-      </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
-        <v>80388</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>327</v>
-      </c>
-    </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A41" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>2</v>
@@ -1759,12 +1697,12 @@
       <c r="E41" s="3" t="n">
         <v>2.34902418148972</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
       <c r="H41" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
+      <c r="I41" s="5"/>
       <c r="J41" s="2" t="n">
         <v>777095</v>
       </c>
@@ -1773,10 +1711,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A42" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>6</v>
@@ -1810,10 +1746,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A43" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1827,10 +1761,10 @@
       <c r="E43" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1839,10 +1773,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A44" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1856,10 +1788,10 @@
       <c r="E44" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1868,68 +1800,70 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
+      <c r="A45" t="str">
+        <v>dairy</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C45" s="3" t="n">
+        <v>1.569724301814138</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1.0957072004937733</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2.249032221705145</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.5201448178624637</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>4.737208367915377</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.028050841105591397</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>512230</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>zinc</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1.736651373180698</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>1.019946879904872</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="2" t="n">
         <v>63257</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>229</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>1.891151114818652</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>1.198753536073191</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>2.871633714999859</v>
-      </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
-        <v>2143</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>323</v>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>omega_9_fatty_acids</t>
-        </is>
+      <c r="A47" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
@@ -1943,10 +1877,10 @@
       <c r="E47" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="5"/>
       <c r="J47" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1955,47 +1889,35 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A48" t="str">
+        <v>omega_9_fatty_acids</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.217099921035707</v>
+        <v>1.891151114818652</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.236889796360678</v>
+        <v>1.198753536073191</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.973709335859187</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>0.203362121878933</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>24.17132558630012</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0.2259507640863558</v>
-      </c>
+        <v>2.871633714999859</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="5"/>
       <c r="J48" s="2" t="n">
-        <v>19420</v>
+        <v>2143</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1051</v>
+        <v>323</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
+      <c r="A49" t="str">
+        <v>copper</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>2</v>
@@ -2009,12 +1931,12 @@
       <c r="E49" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
       <c r="H49" s="4" t="n">
-        <v>86.43000000000001</v>
-      </c>
-      <c r="I49" s="5" t="inlineStr"/>
+        <v>86.43</v>
+      </c>
+      <c r="I49" s="5"/>
       <c r="J49" s="2" t="n">
         <v>95958</v>
       </c>

--- a/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,8 +509,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>linoleic_acid</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -524,10 +526,10 @@
       <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
@@ -536,8 +538,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>omega_6_fatty_acids</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>omega_6_fatty_acids</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -551,10 +555,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -563,8 +567,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>selenium</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -578,10 +584,10 @@
       <c r="E4" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>2296</v>
       </c>
@@ -590,8 +596,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>tomato</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -605,10 +613,10 @@
       <c r="E5" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
@@ -617,8 +625,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>green_tea</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -632,12 +642,12 @@
       <c r="E6" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="2" t="n">
         <v>103012</v>
       </c>
@@ -646,8 +656,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>quercetin</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -661,10 +673,10 @@
       <c r="E7" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
@@ -673,8 +685,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>plant_protein_intake</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>plant_protein_intake</t>
+        </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -688,10 +702,10 @@
       <c r="E8" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="2" t="n">
         <v>87841</v>
       </c>
@@ -700,8 +714,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>eggs</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -715,10 +731,10 @@
       <c r="E9" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="2" t="n">
         <v>1812</v>
       </c>
@@ -727,8 +743,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>vitamin_e</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>4</v>
@@ -749,10 +767,10 @@
         <v>3.723705085890995</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>75.49</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.4983024239643537</v>
+        <v>0.498302423964353</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>127855</v>
@@ -762,8 +780,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>anti_inflammatory_diet</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -777,10 +797,10 @@
       <c r="E11" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="2" t="n">
         <v>71421</v>
       </c>
@@ -789,8 +809,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>tea</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>5</v>
@@ -814,7 +836,7 @@
         <v>70.23</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.3215564042344249</v>
+        <v>0.3215564042344246</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>907106</v>
@@ -824,8 +846,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>folic_acid</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -839,12 +863,12 @@
       <c r="E13" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
@@ -853,8 +877,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>alcohol</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>27</v>
@@ -869,7 +895,7 @@
         <v>0.8253894033052035</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.5066166105770156</v>
+        <v>0.5066166105770157</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>1.110045220411901</v>
@@ -888,8 +914,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>beta_carotene</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
@@ -913,7 +941,7 @@
         <v>53.56</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.9064511286620557</v>
+        <v>0.9064511286620555</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>881922</v>
@@ -923,8 +951,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>vitamin_c</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
@@ -958,8 +988,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>lutein</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
@@ -993,8 +1025,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>betaine</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1008,10 +1042,10 @@
       <c r="E18" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1020,8 +1054,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>choline</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1035,10 +1071,10 @@
       <c r="E19" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="5"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1047,8 +1083,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>vitamin_d</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1062,12 +1100,12 @@
       <c r="E20" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
         <v>4112</v>
       </c>
@@ -1076,8 +1114,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>zeaxanthin</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>2</v>
@@ -1091,12 +1131,12 @@
       <c r="E21" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1105,8 +1145,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>vitamin_b3</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1120,10 +1162,10 @@
       <c r="E22" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1132,8 +1174,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>lycopene</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>3</v>
@@ -1167,8 +1211,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>vitamin_b6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1182,10 +1228,10 @@
       <c r="E24" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1194,8 +1240,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>total_dietary_fiber_intake</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>3</v>
@@ -1229,8 +1277,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>vitamin_b2</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1244,10 +1294,10 @@
       <c r="E26" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1256,8 +1306,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1271,10 +1323,10 @@
       <c r="E27" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1283,8 +1335,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>polyunsaturated_fat_pufa</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>3</v>
@@ -1305,7 +1359,7 @@
         <v>1611.24360139533</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>93.26</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>0.9220557767202346</v>
@@ -1318,8 +1372,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>animal_protein_intake</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1333,10 +1389,10 @@
       <c r="E29" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="5"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1345,14 +1401,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>calcium</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1.0591852706547322</v>
+        <v>1.059185270654732</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0.9035715319777113</v>
@@ -1361,16 +1419,16 @@
         <v>1.241598919253702</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.37795762072777117</v>
+        <v>0.3779576207356611</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2.9682519310279556</v>
+        <v>2.968251930965993</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.9149861270491104</v>
+        <v>0.9149861270491101</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>494621</v>
@@ -1380,8 +1438,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>vitamin_b1</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>2</v>
@@ -1395,12 +1455,12 @@
       <c r="E31" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="4" t="n">
-        <v>85.51</v>
-      </c>
-      <c r="I31" s="5"/>
+        <v>85.51000000000001</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1409,14 +1469,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.1271586532561868</v>
+        <v>1.127158653256187</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0.9770670508204692</v>
@@ -1425,16 +1487,16 @@
         <v>1.300176468168491</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.6378314879402918</v>
+        <v>0.6378314879357913</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.9918844610713744</v>
+        <v>1.991884461085429</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>75.14</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.10245798863837999</v>
+        <v>0.10245798863838</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>599592</v>
@@ -1444,8 +1506,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>processed_meat_intake</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>6</v>
@@ -1466,7 +1530,7 @@
         <v>2.09765466731294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>77.04</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0.009426052809354803</v>
@@ -1479,32 +1543,34 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>ultra_processed_food_intake</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.1812816581299752</v>
+        <v>1.181281658129975</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.0754078661566628</v>
+        <v>1.075407866156663</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.2975787138523882</v>
+        <v>1.297578713852388</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.6427321484843646</v>
+        <v>0.6427321484922891</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2.171085356668214</v>
+        <v>2.171085356641445</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.21970887695697142</v>
+        <v>0.2197088769569714</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1127884</v>
@@ -1514,8 +1580,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>vitamin_a</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1529,12 +1597,12 @@
       <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>92.65</v>
-      </c>
-      <c r="I35" s="5"/>
+        <v>92.65000000000001</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1543,8 +1611,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>manganese</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>manganese</t>
+        </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1558,10 +1628,10 @@
       <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
@@ -1570,14 +1640,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>non_nutritive_sweetener_intake</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>non_nutritive_sweetener_intake</t>
+        </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.2763443304894546</v>
+        <v>1.276344330489455</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0.9973036417217132</v>
@@ -1585,12 +1657,12 @@
       <c r="E37" s="3" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
         <v>115981</v>
       </c>
@@ -1599,8 +1671,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>potassium</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1614,10 +1688,10 @@
       <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1626,8 +1700,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>dietary_protein_intake</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -1641,12 +1717,12 @@
       <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>66.46</v>
-      </c>
-      <c r="I39" s="5"/>
+        <v>66.45999999999999</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1655,8 +1731,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>yogurt</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1670,10 +1748,10 @@
       <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1682,8 +1760,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>monounsaturated_fat_mufa</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>2</v>
@@ -1697,12 +1777,12 @@
       <c r="E41" s="3" t="n">
         <v>2.34902418148972</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I41" s="5"/>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="2" t="n">
         <v>777095</v>
       </c>
@@ -1711,8 +1791,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>red_meat</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>6</v>
@@ -1736,7 +1818,7 @@
         <v>81.78</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.01747970235970359</v>
+        <v>0.01747970235970358</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>1768446</v>
@@ -1746,8 +1828,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>docosahexaenoic_acid</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1761,10 +1845,10 @@
       <c r="E43" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1773,8 +1857,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>omega_3_fatty_acids</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1788,10 +1874,10 @@
       <c r="E44" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="5"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1800,8 +1886,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>dairy</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>6</v>
@@ -1810,22 +1898,22 @@
         <v>1.569724301814138</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.0957072004937733</v>
+        <v>1.095707200493773</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>2.249032221705145</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.5201448178624637</v>
+        <v>0.5201448178624649</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>4.737208367915377</v>
+        <v>4.737208367915367</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>72.14</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.028050841105591397</v>
+        <v>0.02805084110559141</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>512230</v>
@@ -1835,8 +1923,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>zinc</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -1850,10 +1940,10 @@
       <c r="E46" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="2" t="n">
         <v>63257</v>
       </c>
@@ -1862,8 +1952,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>oleic_acid</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
@@ -1877,10 +1969,10 @@
       <c r="E47" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="5"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1889,8 +1981,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>omega_9_fatty_acids</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>omega_9_fatty_acids</t>
+        </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
@@ -1904,10 +1998,10 @@
       <c r="E48" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="5"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1916,8 +2010,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>copper</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
       </c>
       <c r="B49" s="2" t="n">
         <v>2</v>
@@ -1931,12 +2027,12 @@
       <c r="E49" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>86.43</v>
-      </c>
-      <c r="I49" s="5"/>
+        <v>86.43000000000001</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="2" t="n">
         <v>95958</v>
       </c>

--- a/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A2" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>omega_6_fatty_acids</t>
-        </is>
+      <c r="A3" t="str">
+        <v>omega_6_fatty_acids</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A4" t="str">
+        <v>selenium</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -584,10 +578,10 @@
       <c r="E4" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>2296</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A5" t="str">
+        <v>tomato</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -613,10 +605,10 @@
       <c r="E5" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
@@ -625,10 +617,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A6" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -642,12 +632,12 @@
       <c r="E6" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
       <c r="H6" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>103012</v>
       </c>
@@ -656,10 +646,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A7" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -673,10 +661,10 @@
       <c r="E7" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
@@ -685,10 +673,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>plant_protein_intake</t>
-        </is>
+      <c r="A8" t="str">
+        <v>plant_protein_intake</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -702,10 +688,10 @@
       <c r="E8" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>87841</v>
       </c>
@@ -714,10 +700,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A9" t="str">
+        <v>eggs</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -731,10 +715,10 @@
       <c r="E9" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="2" t="n">
         <v>1812</v>
       </c>
@@ -743,10 +727,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A10" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>4</v>
@@ -767,7 +749,7 @@
         <v>3.723705085890995</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>75.48999999999999</v>
+        <v>75.49</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0.498302423964353</v>
@@ -780,10 +762,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A11" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -797,10 +777,10 @@
       <c r="E11" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="2" t="n">
         <v>71421</v>
       </c>
@@ -809,10 +789,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A12" t="str">
+        <v>tea</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>5</v>
@@ -846,10 +824,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A13" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -863,12 +839,12 @@
       <c r="E13" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
@@ -877,47 +853,43 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A14" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.7499115595537207</v>
+        <v>0.7484880803240668</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.6812676670885198</v>
+        <v>0.6809952145158317</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.8253894033052035</v>
+        <v>0.8226701075800033</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.5066166105770157</v>
+        <v>0.5070170678198778</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.110045220411901</v>
+        <v>1.1049616313631374</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>77.52</v>
+        <v>76.85</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.001819124570496827</v>
+        <v>0.0013200939393045895</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14136959</v>
+        <v>14214219</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>29867</v>
+        <v>30116</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A15" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
@@ -951,10 +923,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A16" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
@@ -988,10 +958,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A17" t="str">
+        <v>lutein</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
@@ -1025,10 +993,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A18" t="str">
+        <v>betaine</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1042,10 +1008,10 @@
       <c r="E18" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1054,10 +1020,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A19" t="str">
+        <v>choline</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1071,10 +1035,10 @@
       <c r="E19" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1083,10 +1047,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A20" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1100,12 +1062,12 @@
       <c r="E20" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>4112</v>
       </c>
@@ -1114,10 +1076,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A21" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>2</v>
@@ -1131,12 +1091,12 @@
       <c r="E21" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
       <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1145,10 +1105,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A22" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1162,10 +1120,10 @@
       <c r="E22" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1174,10 +1132,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A23" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>3</v>
@@ -1211,10 +1167,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A24" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1228,10 +1182,10 @@
       <c r="E24" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1240,10 +1194,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A25" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>3</v>
@@ -1277,10 +1229,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A26" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1294,10 +1244,10 @@
       <c r="E26" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1306,10 +1256,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A27" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1323,10 +1271,10 @@
       <c r="E27" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1335,10 +1283,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A28" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>3</v>
@@ -1359,7 +1305,7 @@
         <v>1611.24360139533</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>93.26000000000001</v>
+        <v>93.26</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>0.9220557767202346</v>
@@ -1372,10 +1318,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A29" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1389,10 +1333,10 @@
       <c r="E29" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="5"/>
       <c r="J29" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1401,10 +1345,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A30" t="str">
+        <v>calcium</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>3</v>
@@ -1438,10 +1380,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A31" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>2</v>
@@ -1455,12 +1395,12 @@
       <c r="E31" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="4" t="n">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="I31" s="5" t="inlineStr"/>
+        <v>85.51</v>
+      </c>
+      <c r="I31" s="5"/>
       <c r="J31" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1469,10 +1409,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A32" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>4</v>
@@ -1506,10 +1444,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A33" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>6</v>
@@ -1530,7 +1466,7 @@
         <v>2.09765466731294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>77.04000000000001</v>
+        <v>77.04</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0.009426052809354803</v>
@@ -1543,10 +1479,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
+      <c r="A34" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>3</v>
@@ -1580,10 +1514,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A35" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1597,12 +1529,12 @@
       <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="4" t="n">
-        <v>92.65000000000001</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
+        <v>92.65</v>
+      </c>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1611,10 +1543,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>manganese</t>
-        </is>
+      <c r="A36" t="str">
+        <v>manganese</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1628,10 +1558,10 @@
       <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
@@ -1640,10 +1570,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>non_nutritive_sweetener_intake</t>
-        </is>
+      <c r="A37" t="str">
+        <v>non_nutritive_sweetener_intake</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -1657,12 +1585,12 @@
       <c r="E37" s="3" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="I37" s="5"/>
       <c r="J37" s="2" t="n">
         <v>115981</v>
       </c>
@@ -1671,10 +1599,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A38" t="str">
+        <v>potassium</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1688,10 +1614,10 @@
       <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1700,10 +1626,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A39" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -1717,12 +1641,12 @@
       <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="4" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
+        <v>66.46</v>
+      </c>
+      <c r="I39" s="5"/>
       <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1731,10 +1655,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A40" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1748,10 +1670,10 @@
       <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1760,10 +1682,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A41" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>2</v>
@@ -1777,12 +1697,12 @@
       <c r="E41" s="3" t="n">
         <v>2.34902418148972</v>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
       <c r="H41" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
+      <c r="I41" s="5"/>
       <c r="J41" s="2" t="n">
         <v>777095</v>
       </c>
@@ -1791,10 +1711,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A42" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>6</v>
@@ -1828,10 +1746,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A43" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1845,10 +1761,10 @@
       <c r="E43" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1857,10 +1773,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A44" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1</v>
@@ -1874,10 +1788,10 @@
       <c r="E44" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1886,10 +1800,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A45" t="str">
+        <v>dairy</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>6</v>
@@ -1923,10 +1835,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
+      <c r="A46" t="str">
+        <v>zinc</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -1940,10 +1850,10 @@
       <c r="E46" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
       <c r="J46" s="2" t="n">
         <v>63257</v>
       </c>
@@ -1952,10 +1862,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A47" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>1</v>
@@ -1969,10 +1877,10 @@
       <c r="E47" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="5"/>
       <c r="J47" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1981,10 +1889,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>omega_9_fatty_acids</t>
-        </is>
+      <c r="A48" t="str">
+        <v>omega_9_fatty_acids</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>1</v>
@@ -1998,10 +1904,10 @@
       <c r="E48" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="5"/>
       <c r="J48" s="2" t="n">
         <v>2143</v>
       </c>
@@ -2010,10 +1916,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
+      <c r="A49" t="str">
+        <v>copper</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>2</v>
@@ -2027,12 +1931,12 @@
       <c r="E49" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
       <c r="H49" s="4" t="n">
-        <v>86.43000000000001</v>
-      </c>
-      <c r="I49" s="5" t="inlineStr"/>
+        <v>86.43</v>
+      </c>
+      <c r="I49" s="5"/>
       <c r="J49" s="2" t="n">
         <v>95958</v>
       </c>

--- a/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -450,1497 +462,1593 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>linoleic_acid</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.4012516644420606</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>omega_6_fatty_acids</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>omega_6_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.4012516644420606</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>selenium</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.3344926849794722</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>2296</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>1142</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>tomato</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.3111160697883123</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>672</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>green_tea</v>
-      </c>
-      <c r="B6" s="2" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.5124767166133164</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.2367619672848031</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
         <v>83.87</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="2" t="n">
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>103012</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>536</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>quercetin</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0.6006253983961163</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.4006256157623534</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="2" t="n">
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
         <v>27111</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>228</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>plant_protein_intake</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>plant_protein_intake</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.610619915389884</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.4506451102042392</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="2" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
         <v>87841</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>457</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>eggs</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.4813011881361022</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="2" t="n">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>vitamin_e</v>
-      </c>
-      <c r="B10" s="2" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>0.6712591513204014</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.4539809691459988</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.9926273125874261</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>0.1210055140882807</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>3.723705085890995</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>75.49</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0.498302423964353</v>
-      </c>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="n">
+        <v>0.1210055140908499</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>3.723705085811933</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4983024239643532</v>
+      </c>
+      <c r="J10" s="3" t="n">
         <v>127855</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>2404</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>anti_inflammatory_diet</v>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>0.6805669490764156</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.5206505047421757</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>71421</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>tea</v>
-      </c>
-      <c r="B12" s="2" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.7270936446838011</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.5572730186429885</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>0.9486645691674115</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>0.2961113832763807</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>1.785359151985504</v>
-      </c>
-      <c r="H12" s="4" t="n">
+      <c r="F12" s="4" t="n">
+        <v>0.2961113832763343</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1.785359151985784</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>70.23</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="6" t="n">
         <v>0.3215564042344246</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="3" t="n">
         <v>907106</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>3147</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>folic_acid</v>
-      </c>
-      <c r="B13" s="2" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>0.7353563995110923</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.5173167100803437</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
         <v>49.41</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="2" t="n">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>alcohol</v>
-      </c>
-      <c r="B14" s="2" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>0.7484880803240668</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.6809952145158317</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.8226701075800033</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0.5070170678198778</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>1.1049616313631374</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>76.85</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>0.0013200939393045895</v>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="4" t="n">
+        <v>0.507017067819878</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1.104961631363137</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.001320093939304585</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>14214219</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>30116</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>beta_carotene</v>
-      </c>
-      <c r="B15" s="2" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>0.7557081668603727</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.6375643919946457</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>0.8956549863849572</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0.4498278062406948</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>1.269585440331544</v>
-      </c>
-      <c r="H15" s="4" t="n">
+      <c r="F15" s="4" t="n">
+        <v>0.4498278062406541</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1.269585440331658</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>53.56</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0.9064511286620555</v>
-      </c>
-      <c r="J15" s="2" t="n">
+      <c r="I15" s="6" t="n">
+        <v>0.9064511286620556</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>vitamin_c</v>
-      </c>
-      <c r="B16" s="2" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.7590406087904665</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.6146514007082959</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>0.9373486257886696</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0.4240450272610667</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>1.358682707622687</v>
-      </c>
-      <c r="H16" s="4" t="n">
+      <c r="F16" s="4" t="n">
+        <v>0.4240450272610237</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1.358682707622825</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>38.94</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>0.297720986509244</v>
-      </c>
-      <c r="J16" s="2" t="n">
+      <c r="I16" s="6" t="n">
+        <v>0.2977209865092436</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>128222</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>2559</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>lutein</v>
-      </c>
-      <c r="B17" s="2" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>0.7716686738745262</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.6812676670885198</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.8741528788765721</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0.630272139746614</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.9447863941418472</v>
-      </c>
-      <c r="H17" s="4" t="n">
+      <c r="F17" s="4" t="n">
+        <v>0.6302721397465917</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.9447863941418806</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0.5550198293102779</v>
-      </c>
-      <c r="J17" s="2" t="n">
+      <c r="I17" s="6" t="n">
+        <v>0.5550198293102784</v>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>betaine</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="n">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="2" t="n">
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>choline</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="2" t="n">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>vitamin_d</v>
-      </c>
-      <c r="B20" s="2" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>0.7892280209121737</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.6555373486867049</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4" t="n">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="2" t="n">
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
         <v>4112</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>776</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>zeaxanthin</v>
-      </c>
-      <c r="B21" s="2" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>0.7908871412226887</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.672266795591652</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4" t="n">
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="2" t="n">
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
         <v>781129</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>2616</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>vitamin_b3</v>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.6012503602491741</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="2" t="n">
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>lycopene</v>
-      </c>
-      <c r="B23" s="2" t="n">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>0.84484677451711</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.5871352951128217</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>1.215675634480141</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>0.01174800814484453</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>60.75634810699317</v>
-      </c>
-      <c r="H23" s="4" t="n">
+      <c r="F23" s="4" t="n">
+        <v>0.01174800814382701</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>60.75634811225537</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>78.69</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I23" s="6" t="n">
         <v>0.1356399865798741</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="3" t="n">
         <v>873444</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>2860</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>vitamin_b6</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="3" t="n">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
         <v>0.8506633898445702</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="2" t="n">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>total_dietary_fiber_intake</v>
-      </c>
-      <c r="B25" s="2" t="n">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>0.8684024671088</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.7781001776863548</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>0.9691847740261416</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>0.3170188386298179</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>2.378795052496037</v>
-      </c>
-      <c r="H25" s="4" t="n">
+      <c r="F25" s="4" t="n">
+        <v>0.3170188386233463</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>2.378795052544597</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>32.39</v>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I25" s="6" t="n">
         <v>0.6347647391470264</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="3" t="n">
         <v>198798</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>2632</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>vitamin_b2</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>0.880549357132928</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.6611687215022507</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="2" t="n">
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>0.920382805616512</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>polyunsaturated_fat_pufa</v>
-      </c>
-      <c r="B28" s="2" t="n">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>0.9440274829178357</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.5226203430689871</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.705230001708038</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>0.0005531056183760294</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>1611.24360139533</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>93.26</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>0.9220557767202346</v>
-      </c>
-      <c r="J28" s="2" t="n">
+      <c r="F28" s="4" t="n">
+        <v>0.0005531056182926397</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1611.243601638252</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.9220557767202349</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>861316</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>2507</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>animal_protein_intake</v>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="3" t="n">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="2" t="n">
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>1019</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>calcium</v>
-      </c>
-      <c r="B30" s="2" t="n">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>1.059185270654732</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.9035715319777113</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>1.241598919253702</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>0.3779576207356611</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>2.968251930965993</v>
-      </c>
-      <c r="H30" s="4" t="n">
+      <c r="F30" s="4" t="n">
+        <v>0.3779576207277712</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>2.968251931027956</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>0.9149861270491101</v>
-      </c>
-      <c r="J30" s="2" t="n">
+      <c r="I30" s="6" t="n">
+        <v>0.9149861270491104</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>494621</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>1367</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>vitamin_b1</v>
-      </c>
-      <c r="B31" s="2" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>1.069616314941161</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.5119644960496699</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4" t="n">
-        <v>85.51</v>
-      </c>
-      <c r="I31" s="5"/>
-      <c r="J31" s="2" t="n">
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
-      </c>
-      <c r="B32" s="2" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>1.127158653256187</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.9770670508204692</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>1.300176468168491</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>0.6378314879357913</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.991884461085429</v>
-      </c>
-      <c r="H32" s="4" t="n">
+      <c r="F32" s="4" t="n">
+        <v>0.6378314879402918</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1.991884461071374</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>75.14</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" s="6" t="n">
         <v>0.10245798863838</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="3" t="n">
         <v>599592</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>1649</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>processed_meat_intake</v>
-      </c>
-      <c r="B33" s="2" t="n">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>1.149239018159417</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.9369737613162469</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1.409591575973965</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>0.6296319129363084</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>2.09765466731294</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>77.04</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0.009426052809354803</v>
-      </c>
-      <c r="J33" s="2" t="n">
+      <c r="F33" s="4" t="n">
+        <v>0.6296319129363077</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>2.097654667312942</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.009426052809354796</v>
+      </c>
+      <c r="J33" s="3" t="n">
         <v>1766660</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>5212</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>ultra_processed_food_intake</v>
-      </c>
-      <c r="B34" s="2" t="n">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>1.181281658129975</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>1.075407866156663</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>1.297578713852388</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0.6427321484922891</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>2.171085356641445</v>
-      </c>
-      <c r="H34" s="4" t="n">
+      <c r="F34" s="4" t="n">
+        <v>0.6427321484843646</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2.171085356668214</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="I34" s="6" t="n">
         <v>0.2197088769569714</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="3" t="n">
         <v>1127884</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>4245</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>vitamin_a</v>
-      </c>
-      <c r="B35" s="2" t="n">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>1.225562595253664</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.5280311504245172</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4" t="n">
-        <v>92.65</v>
-      </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="2" t="n">
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>manganese</v>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="3" t="n">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>manganese</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="n">
         <v>1.259147309219077</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.8303675352604869</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="2" t="n">
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
         <v>61321</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>229</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>non_nutritive_sweetener_intake</v>
-      </c>
-      <c r="B37" s="2" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>non_nutritive_sweetener_intake</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>1.276344330489455</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.9973036417217132</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4" t="n">
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="3" t="n">
         <v>115981</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>473</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>potassium</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="n">
         <v>1.279067174104721</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>0.8702945807931509</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="2" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>120852</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="3" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>dietary_protein_intake</v>
-      </c>
-      <c r="B39" s="2" t="n">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>1.302388647984454</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>0.7565399032150474</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4" t="n">
-        <v>66.46</v>
-      </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="2" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>776349</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>yogurt</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>1.307892083408092</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>1.029839375952533</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="2" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>monounsaturated_fat_mufa</v>
-      </c>
-      <c r="B41" s="2" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>1.388466637849501</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>0.8207801406277248</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>2.34902418148972</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="4" t="n">
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="n">
         <v>80.2</v>
       </c>
-      <c r="I41" s="5"/>
-      <c r="J41" s="2" t="n">
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
         <v>777095</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>1801</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>red_meat</v>
-      </c>
-      <c r="B42" s="2" t="n">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>1.431037921180599</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>1.128286375676676</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>1.815207887998699</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>0.6713010778247132</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>3.050597711674792</v>
-      </c>
-      <c r="H42" s="4" t="n">
+      <c r="F42" s="4" t="n">
+        <v>0.6713010778247123</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>3.050597711674797</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>81.78</v>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>0.01747970235970358</v>
-      </c>
-      <c r="J42" s="2" t="n">
+      <c r="I42" s="6" t="n">
+        <v>0.0174797023597036</v>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>1768446</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>5800</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>docosahexaenoic_acid</v>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="3" t="n">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="2" t="n">
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>omega_3_fatty_acids</v>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="3" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="2" t="n">
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>dairy</v>
-      </c>
-      <c r="B45" s="2" t="n">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="4" t="n">
         <v>1.569724301814138</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>1.095707200493773</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>2.249032221705145</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>0.5201448178624649</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>4.737208367915367</v>
-      </c>
-      <c r="H45" s="4" t="n">
+      <c r="F45" s="4" t="n">
+        <v>0.5201448178624637</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>4.737208367915377</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>72.14</v>
       </c>
-      <c r="I45" s="5" t="n">
-        <v>0.02805084110559141</v>
-      </c>
-      <c r="J45" s="2" t="n">
+      <c r="I45" s="6" t="n">
+        <v>0.0280508411055914</v>
+      </c>
+      <c r="J45" s="3" t="n">
         <v>512230</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>2409</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>zinc</v>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="n">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="n">
         <v>1.736651373180698</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>1.019946879904872</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="2" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>63257</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>229</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>oleic_acid</v>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="3" t="n">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="n">
         <v>1.891151114818652</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>1.198753536073191</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="2" t="n">
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="3" t="n">
         <v>2143</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
-        <v>omega_9_fatty_acids</v>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="n">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>omega_9_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="n">
         <v>1.891151114818652</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="4" t="n">
         <v>1.198753536073191</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="4" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="2" t="n">
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="3" t="n">
         <v>2143</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K48" s="3" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v>copper</v>
-      </c>
-      <c r="B49" s="2" t="n">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="4" t="n">
         <v>2.441469226259395</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="4" t="n">
         <v>0.4308048825855873</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="4" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="4" t="n">
-        <v>86.43</v>
-      </c>
-      <c r="I49" s="5"/>
-      <c r="J49" s="2" t="n">
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="3" t="n">
         <v>95958</v>
       </c>
-      <c r="K49" s="2" t="n">
+      <c r="K49" s="3" t="n">
         <v>353</v>
       </c>
     </row>

--- a/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/yes/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,26 +514,26 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.4012516644420606</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -555,26 +543,26 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.4012516644420606</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -584,26 +572,26 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.3344926849794722</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>2296</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>1142</v>
       </c>
     </row>
@@ -613,26 +601,26 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.3111160697883123</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>672</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>335</v>
       </c>
     </row>
@@ -642,28 +630,28 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>0.5124767166133164</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.2367619672848031</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>103012</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>536</v>
       </c>
     </row>
@@ -673,26 +661,26 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.6006253983961163</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.4006256157623534</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
         <v>27111</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>228</v>
       </c>
     </row>
@@ -702,26 +690,26 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.610619915389884</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.4506451102042392</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="3" t="n">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>87841</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>457</v>
       </c>
     </row>
@@ -731,26 +719,26 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.4813011881361022</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="3" t="n">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -760,34 +748,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="3" t="n">
         <v>0.6712591513204014</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.4539809691459988</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.9926273125874261</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>0.1210055140908499</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>3.723705085811933</v>
-      </c>
-      <c r="H10" s="5" t="n">
+      <c r="F10" s="3" t="n">
+        <v>0.1210055140882807</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>3.723705085890995</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>75.48999999999999</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>0.4983024239643532</v>
-      </c>
-      <c r="J10" s="3" t="n">
+      <c r="I10" s="5" t="n">
+        <v>0.4983024239643531</v>
+      </c>
+      <c r="J10" s="2" t="n">
         <v>127855</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>2404</v>
       </c>
     </row>
@@ -797,26 +785,26 @@
           <t>anti_inflammatory_diet</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.6805669490764156</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.5206505047421757</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="3" t="n">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
         <v>71421</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>431</v>
       </c>
     </row>
@@ -826,34 +814,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <v>0.7270936446838011</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.5572730186429885</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>0.9486645691674115</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0.2961113832763343</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1.785359151985784</v>
-      </c>
-      <c r="H12" s="5" t="n">
+      <c r="F12" s="3" t="n">
+        <v>0.2961113832763807</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1.785359151985504</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>70.23</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="5" t="n">
         <v>0.3215564042344246</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="2" t="n">
         <v>907106</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>3147</v>
       </c>
     </row>
@@ -863,28 +851,28 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="3" t="n">
         <v>0.7353563995110923</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.5173167100803437</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -894,34 +882,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="3" t="n">
         <v>0.7484880803240668</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.6809952145158317</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.8226701075800033</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0.507017067819878</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1.104961631363137</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="F14" s="3" t="n">
+        <v>0.5070170678198777</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1.104961631363138</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>76.84999999999999</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>0.001320093939304585</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="I14" s="5" t="n">
+        <v>0.001320093939304584</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>14214219</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>30116</v>
       </c>
     </row>
@@ -931,34 +919,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>0.7557081668603727</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.6375643919946457</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.8956549863849572</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>0.4498278062406541</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1.269585440331658</v>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="F15" s="3" t="n">
+        <v>0.4498278062406948</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1.269585440331544</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>53.56</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <v>0.9064511286620556</v>
-      </c>
-      <c r="J15" s="3" t="n">
+      <c r="I15" s="5" t="n">
+        <v>0.9064511286620555</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -968,34 +956,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.7590406087904665</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.6146514007082959</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>0.9373486257886696</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0.4240450272610237</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1.358682707622825</v>
-      </c>
-      <c r="H16" s="5" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0.4240450272610667</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1.358682707622687</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>38.94</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>0.2977209865092436</v>
-      </c>
-      <c r="J16" s="3" t="n">
+      <c r="I16" s="5" t="n">
+        <v>0.297720986509244</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>128222</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>2559</v>
       </c>
     </row>
@@ -1005,34 +993,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="3" t="n">
         <v>0.7716686738745262</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.6812676670885198</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.8741528788765721</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>0.6302721397465917</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0.9447863941418806</v>
-      </c>
-      <c r="H17" s="5" t="n">
+      <c r="F17" s="3" t="n">
+        <v>0.630272139746614</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.9447863941418472</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="6" t="n">
-        <v>0.5550198293102784</v>
-      </c>
-      <c r="J17" s="3" t="n">
+      <c r="I17" s="5" t="n">
+        <v>0.5550198293102783</v>
+      </c>
+      <c r="J17" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -1042,26 +1030,26 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="n">
+      <c r="B18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="3" t="n">
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1071,26 +1059,26 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="n">
+      <c r="B19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1100,28 +1088,28 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="3" t="n">
         <v>0.7892280209121737</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.6555373486867049</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="n">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="3" t="n">
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>4112</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>776</v>
       </c>
     </row>
@@ -1131,28 +1119,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.7908871412226887</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.672266795591652</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="5" t="n">
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="3" t="n">
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
         <v>781129</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>2616</v>
       </c>
     </row>
@@ -1162,26 +1150,26 @@
           <t>vitamin_b3</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="n">
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.6012503602491741</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="3" t="n">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1191,34 +1179,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="3" t="n">
         <v>0.84484677451711</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.5871352951128217</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>1.215675634480141</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>0.01174800814382701</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>60.75634811225537</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="F23" s="3" t="n">
+        <v>0.01174800814484453</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>60.75634810699317</v>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>78.69</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="5" t="n">
         <v>0.1356399865798741</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="J23" s="2" t="n">
         <v>873444</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>2860</v>
       </c>
     </row>
@@ -1228,26 +1216,26 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="n">
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>0.8506633898445702</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="3" t="n">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1257,34 +1245,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="3" t="n">
         <v>0.8684024671088</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.7781001776863548</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="3" t="n">
         <v>0.9691847740261416</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>0.3170188386233463</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>2.378795052544597</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="F25" s="3" t="n">
+        <v>0.3170188386298179</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2.378795052496037</v>
+      </c>
+      <c r="H25" s="4" t="n">
         <v>32.39</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="5" t="n">
         <v>0.6347647391470264</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="J25" s="2" t="n">
         <v>198798</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>2632</v>
       </c>
     </row>
@@ -1294,26 +1282,26 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.880549357132928</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.6611687215022507</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1323,26 +1311,26 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.920382805616512</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1352,34 +1340,34 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="3" t="n">
         <v>0.9440274829178357</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.5226203430689871</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.705230001708038</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>0.0005531056182926397</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1611.243601638252</v>
-      </c>
-      <c r="H28" s="5" t="n">
+      <c r="F28" s="3" t="n">
+        <v>0.0005531056183760294</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>1611.24360139533</v>
+      </c>
+      <c r="H28" s="4" t="n">
         <v>93.26000000000001</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>0.9220557767202349</v>
-      </c>
-      <c r="J28" s="3" t="n">
+      <c r="I28" s="5" t="n">
+        <v>0.9220557767202346</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>861316</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>2507</v>
       </c>
     </row>
@@ -1389,26 +1377,26 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4" t="n">
+      <c r="B29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="3" t="n">
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>1019</v>
       </c>
     </row>
@@ -1418,34 +1406,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="3" t="n">
         <v>1.059185270654732</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.9035715319777113</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>1.241598919253702</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>0.3779576207277712</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>2.968251931027956</v>
-      </c>
-      <c r="H30" s="5" t="n">
+      <c r="F30" s="3" t="n">
+        <v>0.3779576207356611</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2.968251930965993</v>
+      </c>
+      <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="6" t="n">
-        <v>0.9149861270491104</v>
-      </c>
-      <c r="J30" s="3" t="n">
+      <c r="I30" s="5" t="n">
+        <v>0.9149861270491101</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <v>494621</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>1367</v>
       </c>
     </row>
@@ -1455,28 +1443,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="3" t="n">
         <v>1.069616314941161</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.5119644960496699</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="5" t="n">
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="3" t="n">
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -1486,34 +1474,34 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>1.127158653256187</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.9770670508204692</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>1.300176468168491</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>0.6378314879402918</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1.991884461071374</v>
-      </c>
-      <c r="H32" s="5" t="n">
+      <c r="F32" s="3" t="n">
+        <v>0.6378314879357913</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.991884461085429</v>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>75.14</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="5" t="n">
         <v>0.10245798863838</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="J32" s="2" t="n">
         <v>599592</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>1649</v>
       </c>
     </row>
@@ -1523,34 +1511,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>1.149239018159417</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.9369737613162469</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.409591575973965</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>0.6296319129363077</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>2.097654667312942</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="F33" s="3" t="n">
+        <v>0.6296319129363084</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>2.09765466731294</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>77.04000000000001</v>
       </c>
-      <c r="I33" s="6" t="n">
-        <v>0.009426052809354796</v>
-      </c>
-      <c r="J33" s="3" t="n">
+      <c r="I33" s="5" t="n">
+        <v>0.009426052809354803</v>
+      </c>
+      <c r="J33" s="2" t="n">
         <v>1766660</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>5212</v>
       </c>
     </row>
@@ -1560,34 +1548,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>1.181281658129975</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>1.075407866156663</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>1.297578713852388</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>0.6427321484843646</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>2.171085356668214</v>
-      </c>
-      <c r="H34" s="5" t="n">
+      <c r="F34" s="3" t="n">
+        <v>0.6427321484922891</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.171085356641445</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="5" t="n">
         <v>0.2197088769569714</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="J34" s="2" t="n">
         <v>1127884</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>4245</v>
       </c>
     </row>
@@ -1597,28 +1585,28 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="3" t="n">
         <v>1.225562595253664</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.5280311504245172</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="n">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
         <v>92.65000000000001</v>
       </c>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="3" t="n">
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -1628,26 +1616,26 @@
           <t>manganese</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4" t="n">
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>1.259147309219077</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.8303675352604869</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="3" t="n">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>229</v>
       </c>
     </row>
@@ -1657,28 +1645,28 @@
           <t>non_nutritive_sweetener_intake</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>1.276344330489455</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.9973036417217132</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="5" t="n">
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
         <v>115981</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>473</v>
       </c>
     </row>
@@ -1688,26 +1676,26 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="n">
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1.279067174104721</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.8702945807931509</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>485</v>
       </c>
     </row>
@@ -1717,28 +1705,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="3" t="n">
         <v>1.302388647984454</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.7565399032150474</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1748,26 +1736,26 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="n">
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1.307892083408092</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>1.029839375952533</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -1777,28 +1765,28 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="3" t="n">
         <v>1.388466637849501</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.8207801406277248</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>2.34902418148972</v>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="5" t="n">
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="n">
         <v>80.2</v>
       </c>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="3" t="n">
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
         <v>777095</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>1801</v>
       </c>
     </row>
@@ -1808,34 +1796,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="3" t="n">
         <v>1.431037921180599</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>1.128286375676676</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>1.815207887998699</v>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>0.6713010778247123</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>3.050597711674797</v>
-      </c>
-      <c r="H42" s="5" t="n">
+      <c r="F42" s="3" t="n">
+        <v>0.6713010778247132</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>3.050597711674792</v>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>81.78</v>
       </c>
-      <c r="I42" s="6" t="n">
-        <v>0.0174797023597036</v>
-      </c>
-      <c r="J42" s="3" t="n">
+      <c r="I42" s="5" t="n">
+        <v>0.01747970235970358</v>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>1768446</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>5800</v>
       </c>
     </row>
@@ -1845,26 +1833,26 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="n">
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="3" t="n">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1874,26 +1862,26 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4" t="n">
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1903,34 +1891,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="3" t="n">
         <v>1.569724301814138</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>1.095707200493773</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>2.249032221705145</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>0.5201448178624637</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>4.737208367915377</v>
-      </c>
-      <c r="H45" s="5" t="n">
+      <c r="F45" s="3" t="n">
+        <v>0.5201448178624649</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>4.737208367915367</v>
+      </c>
+      <c r="H45" s="4" t="n">
         <v>72.14</v>
       </c>
-      <c r="I45" s="6" t="n">
-        <v>0.0280508411055914</v>
-      </c>
-      <c r="J45" s="3" t="n">
+      <c r="I45" s="5" t="n">
+        <v>0.02805084110559141</v>
+      </c>
+      <c r="J45" s="2" t="n">
         <v>512230</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>2409</v>
       </c>
     </row>
@@ -1940,26 +1928,26 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4" t="n">
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1.736651373180698</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>1.019946879904872</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>63257</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>229</v>
       </c>
     </row>
@@ -1969,26 +1957,26 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="4" t="n">
+      <c r="B47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>1.891151114818652</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>1.198753536073191</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="3" t="n">
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>323</v>
       </c>
     </row>
@@ -1998,26 +1986,26 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="n">
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>1.891151114818652</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="3" t="n">
         <v>1.198753536073191</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="3" t="n">
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="2" t="n">
         <v>323</v>
       </c>
     </row>
@@ -2027,28 +2015,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" s="3" t="n">
         <v>2.441469226259395</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="3" t="n">
         <v>0.4308048825855873</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="5" t="n">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="4" t="n">
         <v>86.43000000000001</v>
       </c>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="3" t="n">
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
         <v>95958</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" s="2" t="n">
         <v>353</v>
       </c>
     </row>
